--- a/AAII_Financials/Quarterly/ZHUZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ZHUZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>ZHUZY</t>
   </si>
@@ -655,76 +655,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -764,8 +768,11 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -805,8 +812,11 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -846,8 +856,11 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,8 +876,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -904,8 +918,11 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,8 +962,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,8 +1006,11 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1027,8 +1050,11 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,8 +1067,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1082,8 +1109,11 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1123,8 +1153,11 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,8 +1173,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1181,8 +1215,11 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1222,8 +1259,11 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1263,8 +1303,11 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1304,8 +1347,11 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1345,8 +1391,11 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,8 +1435,11 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1427,8 +1479,11 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1468,8 +1523,11 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1567,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1611,11 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1655,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,8 +1699,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1673,8 +1743,11 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1714,8 +1787,11 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,8 +1831,11 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1796,54 +1875,60 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +1944,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,377 +1962,405 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>738300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1135100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>959900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>853400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1075100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1426100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1459400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1052200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1484600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1146800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1115100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1028500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1027100</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>659800</v>
+      </c>
+      <c r="E42" s="3">
         <v>43600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>309300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>225100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>441000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>659900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>984300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>637600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>789400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>805800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>835900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>491900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>777300</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3198100</v>
+      </c>
+      <c r="E43" s="3">
         <v>3318100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3343300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3056200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3033800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2808400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2844700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3043800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2730600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2534000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2487100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2361900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2283000</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1441400</v>
+      </c>
+      <c r="E44" s="3">
         <v>1410800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1244700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1330200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1144700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1106000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>967700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>921700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>833100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>840700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>780700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>934400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>891000</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>131600</v>
+      </c>
+      <c r="E45" s="3">
         <v>268800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>124300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>399700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>247500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>459100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>79700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>614200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>87400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>193800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>105700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>351200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>158900</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6170900</v>
+      </c>
+      <c r="E46" s="3">
         <v>6176500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5982000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5864600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5970400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6459400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6361500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6269600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5926400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5521100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5326000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5168000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5139200</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1293300</v>
+      </c>
+      <c r="E47" s="3">
         <v>117300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1469300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>117400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>116000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>115900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>384600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>117700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>109500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>105200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>108100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>100900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>102000</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2251000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2216900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2183800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1833000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1640900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1543400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1532700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1445200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1191900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>948900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>965800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>844400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>799800</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>238900</v>
+      </c>
+      <c r="E49" s="3">
         <v>235600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>236700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>226100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>232000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>216200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>222200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>212200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>211700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>214900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>230200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>196800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>162800</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2400,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,49 +2444,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1505200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>95400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1514400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1390500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>650500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>88000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>758600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>790600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>677200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>675500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>648100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>561200</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,49 +2532,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10436700</v>
+      </c>
+      <c r="E54" s="3">
         <v>10440900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10306000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9769100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9656300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9160300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8878100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9012700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8523100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7632000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>7584200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7098600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6948100</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2596,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,254 +2614,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2454400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2425800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2727700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2291800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2180100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2020300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1997400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1885900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1646700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1479800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1517900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1347600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1321600</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E58" s="3">
         <v>17000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>26200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>24700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>19900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>94700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>62600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>82100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>54400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>71900</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>830000</v>
+      </c>
+      <c r="E59" s="3">
         <v>939200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>703900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>923200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1011800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>752800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>502400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>578300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>567700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>389000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>284500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>309700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>334900</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3428500</v>
+      </c>
+      <c r="E60" s="3">
         <v>3436300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3510000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3296100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3295900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2825600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2566000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2548900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2380900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1999200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1927800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1763600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1782700</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E61" s="3">
         <v>53100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>49700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>30600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>32200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>34700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>34200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>81300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>117700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>151300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>116900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>122600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>61200</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E62" s="3">
         <v>115800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>97500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>122800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>124100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>99600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>84300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>96300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>100100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>80500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>86800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>54400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>48300</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +2920,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +2964,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,49 +3008,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3679400</v>
+      </c>
+      <c r="E66" s="3">
         <v>3684300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3740100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3511400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3513700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3019700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2745500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2795200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2669000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2336700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2246600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2052000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2016100</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3072,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3114,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3158,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3034,8 +3202,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,49 +3246,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4502200</v>
+      </c>
+      <c r="E72" s="3">
         <v>4410200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4257000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3989100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3901200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3895200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3786000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3779000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3510900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3555900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3530200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3296800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3193000</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3334,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3378,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,49 +3422,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6242800</v>
+      </c>
+      <c r="E76" s="3">
         <v>6253800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6074400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5774300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5674700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5687000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5689400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5779500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5438200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5176000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5217700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4916300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4821800</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,54 +3510,60 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3408,8 +3603,11 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,49 +3623,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E83" s="3">
+      <c r="D83" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3">
         <v>132600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>-83000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63200</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3">
         <v>115100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-64200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>54300</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>97000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-53700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3709,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3753,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +3797,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +3841,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,49 +3885,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>352000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-131900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>264200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>33400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>254700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>388500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-18000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>159600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-70500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>423300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>110900</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,49 +3949,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-78300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-92800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-126000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-199900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-160200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-76800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-105700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-124400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-203000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-45800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-204900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-84800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-67800</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4035,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,49 +4079,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-234300</v>
+      </c>
+      <c r="E94" s="3">
         <v>144100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-137900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-60800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-245700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-463400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>175400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-198200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-481900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>57000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-354900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>23100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19300</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,49 +4143,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E96" s="3">
         <v>800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>88000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>190800</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3">
         <v>1300</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>158800</v>
-      </c>
-      <c r="K96" s="3">
-        <v>1000</v>
       </c>
       <c r="L96" s="3">
         <v>1000</v>
       </c>
       <c r="M96" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N96" s="3">
         <v>7400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>103700</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4229,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4273,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,127 +4317,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-107600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-63900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-76100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-183000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>152800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-314000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-257400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>591500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>35400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-73800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>5100</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-51300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>51400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-210000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-303200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>251000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-473700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>269300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>21800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>61300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>97300</v>
       </c>
     </row>
